--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118910567</v>
+        <v>118910561</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551747</v>
+        <v>551765</v>
       </c>
       <c r="R2" t="n">
-        <v>7144337</v>
+        <v>7144391</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -750,7 +766,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +776,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>7 blommande ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +790,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118910550</v>
+        <v>118910562</v>
       </c>
       <c r="B3" t="n">
-        <v>90500</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,30 +821,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551758</v>
+        <v>551767</v>
       </c>
       <c r="R3" t="n">
-        <v>7144433</v>
+        <v>7144393</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -865,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +910,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>fjolårsfruktkropp på död gran</t>
+          <t>20 blommande ex lika många utan blomstängel</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,26 +931,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118910561</v>
+        <v>118910556</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>79601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,43 +960,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -989,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551765</v>
+        <v>551770</v>
       </c>
       <c r="R4" t="n">
-        <v>7144391</v>
+        <v>7144425</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1024,7 +1026,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1036,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>7 blommande ex</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,6 +1053,31 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1067,10 +1094,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118910562</v>
+        <v>118910548</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>90522</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1079,54 +1106,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551767</v>
+        <v>551765</v>
       </c>
       <c r="R5" t="n">
-        <v>7144393</v>
+        <v>7144391</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1158,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1168,12 +1179,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>20 blommande ex lika många utan blomstängel</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,14 +1188,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1206,10 +1206,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118910566</v>
+        <v>118910558</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1218,38 +1218,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551758</v>
+        <v>551738</v>
       </c>
       <c r="R6" t="n">
-        <v>7144433</v>
+        <v>7144298</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1281,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1291,12 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>levande gran</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,8 +1308,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1323,10 +1352,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118910558</v>
+        <v>118910550</v>
       </c>
       <c r="B7" t="n">
-        <v>79601</v>
+        <v>90500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,25 +1364,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1366,10 +1395,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551738</v>
+        <v>551758</v>
       </c>
       <c r="R7" t="n">
-        <v>7144298</v>
+        <v>7144433</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1401,7 +1430,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,12 +1440,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>fjolårsfruktkropp på död gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,22 +1465,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1469,7 +1498,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118910547</v>
+        <v>118910566</v>
       </c>
       <c r="B8" t="n">
         <v>78484</v>
@@ -1509,10 +1538,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551770</v>
+        <v>551758</v>
       </c>
       <c r="R8" t="n">
-        <v>7144425</v>
+        <v>7144433</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1544,7 +1573,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1554,12 +1583,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>levande gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,10 +1615,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118910556</v>
+        <v>118910547</v>
       </c>
       <c r="B9" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1598,31 +1627,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
@@ -1679,7 +1705,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1688,34 +1714,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1732,10 +1732,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118910548</v>
+        <v>118910567</v>
       </c>
       <c r="B10" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1748,21 +1748,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551765</v>
+        <v>551747</v>
       </c>
       <c r="R10" t="n">
-        <v>7144391</v>
+        <v>7144337</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118910561</v>
+        <v>118910566</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,54 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551765</v>
+        <v>551758</v>
       </c>
       <c r="R2" t="n">
-        <v>7144391</v>
+        <v>7144433</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -766,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -776,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>7 blommande ex</t>
+          <t>levande gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +774,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -809,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118910562</v>
+        <v>118910558</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>79608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,43 +804,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -865,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551767</v>
+        <v>551738</v>
       </c>
       <c r="R3" t="n">
-        <v>7144393</v>
+        <v>7144298</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -900,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,12 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>20 blommande ex lika många utan blomstängel</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,6 +901,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -948,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118910556</v>
+        <v>118910561</v>
       </c>
       <c r="B4" t="n">
-        <v>79601</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,30 +950,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -991,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551770</v>
+        <v>551765</v>
       </c>
       <c r="R4" t="n">
-        <v>7144425</v>
+        <v>7144391</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1026,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,12 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>7 blommande ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,31 +1056,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1094,10 +1072,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118910548</v>
+        <v>118910550</v>
       </c>
       <c r="B5" t="n">
-        <v>90522</v>
+        <v>90507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1110,34 +1088,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551765</v>
+        <v>551758</v>
       </c>
       <c r="R5" t="n">
-        <v>7144391</v>
+        <v>7144433</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1169,7 +1150,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,7 +1160,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>fjolårsfruktkropp på död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1188,8 +1174,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1206,10 +1218,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118910558</v>
+        <v>118910562</v>
       </c>
       <c r="B6" t="n">
-        <v>79601</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1218,30 +1230,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1249,10 +1274,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551738</v>
+        <v>551767</v>
       </c>
       <c r="R6" t="n">
-        <v>7144298</v>
+        <v>7144393</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1284,7 +1309,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1319,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>20 blommande ex lika många utan blomstängel</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,26 +1340,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118910550</v>
+        <v>118910547</v>
       </c>
       <c r="B7" t="n">
-        <v>90500</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1368,37 +1373,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551758</v>
+        <v>551770</v>
       </c>
       <c r="R7" t="n">
-        <v>7144433</v>
+        <v>7144425</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1430,7 +1432,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1440,12 +1442,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>fjolårsfruktkropp på död gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,34 +1456,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1498,10 +1474,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118910566</v>
+        <v>118910548</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>90529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1514,21 +1490,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1538,10 +1514,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551758</v>
+        <v>551765</v>
       </c>
       <c r="R8" t="n">
-        <v>7144433</v>
+        <v>7144391</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1573,7 +1549,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1583,12 +1559,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>levande gran</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1615,10 +1586,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118910547</v>
+        <v>118910556</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>79608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1627,28 +1598,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
@@ -1705,7 +1679,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1714,8 +1688,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1735,7 +1735,7 @@
         <v>118910567</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118910566</v>
+        <v>118910561</v>
       </c>
       <c r="B2" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551758</v>
+        <v>551765</v>
       </c>
       <c r="R2" t="n">
-        <v>7144433</v>
+        <v>7144391</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -750,7 +766,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +776,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>levande gran</t>
+          <t>7 blommande ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,6 +790,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118910558</v>
+        <v>118910550</v>
       </c>
       <c r="B3" t="n">
-        <v>79608</v>
+        <v>90507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +821,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551738</v>
+        <v>551758</v>
       </c>
       <c r="R3" t="n">
-        <v>7144298</v>
+        <v>7144433</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -870,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,12 +897,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>fjolårsfruktkropp på död gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,22 +922,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -938,10 +955,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118910561</v>
+        <v>118910547</v>
       </c>
       <c r="B4" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,54 +967,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551765</v>
+        <v>551770</v>
       </c>
       <c r="R4" t="n">
-        <v>7144391</v>
+        <v>7144425</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1029,7 +1030,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1040,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>7 blommande ex</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,7 +1054,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118910550</v>
+        <v>118910562</v>
       </c>
       <c r="B5" t="n">
-        <v>90507</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1084,30 +1084,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1115,10 +1128,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551758</v>
+        <v>551767</v>
       </c>
       <c r="R5" t="n">
-        <v>7144433</v>
+        <v>7144393</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1150,7 +1163,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1160,12 +1173,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>fjolårsfruktkropp på död gran</t>
+          <t>20 blommande ex lika många utan blomstängel</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,26 +1194,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1218,10 +1211,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118910562</v>
+        <v>118910548</v>
       </c>
       <c r="B6" t="n">
-        <v>97853</v>
+        <v>90529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,54 +1223,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551767</v>
+        <v>551765</v>
       </c>
       <c r="R6" t="n">
-        <v>7144393</v>
+        <v>7144391</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1309,7 +1286,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1319,12 +1296,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>20 blommande ex lika många utan blomstängel</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1333,14 +1305,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1357,10 +1323,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118910547</v>
+        <v>118910556</v>
       </c>
       <c r="B7" t="n">
-        <v>78491</v>
+        <v>79608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1369,28 +1335,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
@@ -1447,7 +1416,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1456,8 +1425,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1474,10 +1469,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118910548</v>
+        <v>118910567</v>
       </c>
       <c r="B8" t="n">
-        <v>90529</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1490,21 +1485,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1514,10 +1509,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551765</v>
+        <v>551747</v>
       </c>
       <c r="R8" t="n">
-        <v>7144391</v>
+        <v>7144337</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1549,7 +1544,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1559,7 +1554,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,7 +1581,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118910556</v>
+        <v>118910558</v>
       </c>
       <c r="B9" t="n">
         <v>79608</v>
@@ -1629,10 +1624,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551770</v>
+        <v>551738</v>
       </c>
       <c r="R9" t="n">
-        <v>7144425</v>
+        <v>7144298</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1664,7 +1659,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1674,7 +1669,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1732,7 +1727,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118910567</v>
+        <v>118910566</v>
       </c>
       <c r="B10" t="n">
         <v>78491</v>
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551747</v>
+        <v>551758</v>
       </c>
       <c r="R10" t="n">
-        <v>7144337</v>
+        <v>7144433</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1807,7 +1802,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1817,7 +1812,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>levande gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1323,10 +1323,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118910556</v>
+        <v>118910567</v>
       </c>
       <c r="B7" t="n">
-        <v>79608</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,41 +1335,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551770</v>
+        <v>551747</v>
       </c>
       <c r="R7" t="n">
-        <v>7144425</v>
+        <v>7144337</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1401,7 +1398,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1411,12 +1408,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,34 +1417,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1469,10 +1435,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118910567</v>
+        <v>118910558</v>
       </c>
       <c r="B8" t="n">
-        <v>78491</v>
+        <v>79608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1481,38 +1447,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551747</v>
+        <v>551738</v>
       </c>
       <c r="R8" t="n">
-        <v>7144337</v>
+        <v>7144298</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1544,7 +1513,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1554,7 +1523,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1563,8 +1537,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1581,10 +1581,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118910558</v>
+        <v>118910566</v>
       </c>
       <c r="B9" t="n">
-        <v>79608</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1593,41 +1593,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551738</v>
+        <v>551758</v>
       </c>
       <c r="R9" t="n">
-        <v>7144298</v>
+        <v>7144433</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1659,7 +1656,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1669,12 +1666,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>levande gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,34 +1680,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1727,10 +1698,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118910566</v>
+        <v>118910556</v>
       </c>
       <c r="B10" t="n">
-        <v>78491</v>
+        <v>79608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1739,38 +1710,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551758</v>
+        <v>551770</v>
       </c>
       <c r="R10" t="n">
-        <v>7144433</v>
+        <v>7144425</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1802,7 +1776,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1812,12 +1786,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>levande gran</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1826,8 +1800,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1841,6 +1841,324 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118989667</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90511</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>551747</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7144434</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118989617</v>
+      </c>
+      <c r="B12" t="n">
+        <v>74603</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>551770</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7144431</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118989629</v>
+      </c>
+      <c r="B13" t="n">
+        <v>77428</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>551770</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7144431</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2165,7 +2165,7 @@
         <v>126810186</v>
       </c>
       <c r="B14" t="n">
-        <v>98694</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>126810195</v>
       </c>
       <c r="B15" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>126810193</v>
       </c>
       <c r="B16" t="n">
-        <v>98267</v>
+        <v>98342</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>126810171</v>
       </c>
       <c r="B17" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2165,7 +2165,7 @@
         <v>126810186</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98775</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>126810195</v>
       </c>
       <c r="B15" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>126810193</v>
       </c>
       <c r="B16" t="n">
-        <v>98342</v>
+        <v>98348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>126810171</v>
       </c>
       <c r="B17" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2165,7 +2165,7 @@
         <v>126810186</v>
       </c>
       <c r="B14" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>126810195</v>
       </c>
       <c r="B15" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>126810193</v>
       </c>
       <c r="B16" t="n">
-        <v>98348</v>
+        <v>98349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>126810171</v>
       </c>
       <c r="B17" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2165,7 +2165,7 @@
         <v>126810186</v>
       </c>
       <c r="B14" t="n">
-        <v>98776</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>126810195</v>
       </c>
       <c r="B15" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>126810193</v>
       </c>
       <c r="B16" t="n">
-        <v>98349</v>
+        <v>98353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>126810171</v>
       </c>
       <c r="B17" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2505,7 +2505,7 @@
         <v>126810171</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2165,7 +2165,7 @@
         <v>126810186</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>126810195</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>98353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>126810193</v>
       </c>
       <c r="B16" t="n">
-        <v>98353</v>
+        <v>98342</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>126810171</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>98457</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2165,7 +2165,7 @@
         <v>126810186</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>126810195</v>
       </c>
       <c r="B15" t="n">
-        <v>98353</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>126810193</v>
       </c>
       <c r="B16" t="n">
-        <v>98342</v>
+        <v>98353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>126810171</v>
       </c>
       <c r="B17" t="n">
-        <v>98457</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2621,7 +2621,7 @@
         <v>133851066</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118910550</v>
+        <v>126810193</v>
       </c>
       <c r="B2" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551758</v>
+        <v>551735</v>
       </c>
       <c r="R2" t="n">
-        <v>7144433</v>
+        <v>7144261</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +744,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>04:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>04:49</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>fjolårsfruktkropp på död gran</t>
+          <t>12 överblommade plantor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,34 +773,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -821,53 +791,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118910548</v>
+        <v>126810194</v>
       </c>
       <c r="B3" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551765</v>
+        <v>551774</v>
       </c>
       <c r="R3" t="n">
-        <v>7144391</v>
+        <v>7144275</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,22 +860,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>04:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>04:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>9 överblommade plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,6 +889,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -933,53 +908,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118910547</v>
+        <v>128982914</v>
       </c>
       <c r="B4" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551770</v>
+        <v>551754</v>
       </c>
       <c r="R4" t="n">
-        <v>7144425</v>
+        <v>7144272</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,29 +983,24 @@
           <t>Dorotea</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>AC-Dor-0171</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:09</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:09</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>12 överblommade plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,13 +1009,14 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1046,59 +1024,45 @@
           <t>Eva Mårtensson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118910561</v>
+        <v>118910550</v>
       </c>
       <c r="B5" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1106,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551765</v>
+        <v>551758</v>
       </c>
       <c r="R5" t="n">
-        <v>7144391</v>
+        <v>7144433</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1141,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1151,12 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>7 blommande ex</t>
+          <t>fjolårsfruktkropp på död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,6 +1132,31 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1184,55 +1173,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118910562</v>
+        <v>118989667</v>
       </c>
       <c r="B6" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1240,13 +1211,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551767</v>
+        <v>551747</v>
       </c>
       <c r="R6" t="n">
-        <v>7144393</v>
+        <v>7144434</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1270,27 +1241,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:23</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>20 blommande ex lika många utan blomstängel</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,73 +1259,66 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118910567</v>
+        <v>126810169</v>
       </c>
       <c r="B7" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551747</v>
+        <v>551783</v>
       </c>
       <c r="R7" t="n">
-        <v>7144337</v>
+        <v>7144380</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1393,22 +1342,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,8 +1371,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1435,56 +1405,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118910556</v>
+        <v>126810173</v>
       </c>
       <c r="B8" t="n">
-        <v>79628</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551770</v>
+        <v>551777</v>
       </c>
       <c r="R8" t="n">
-        <v>7144425</v>
+        <v>7144328</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1508,27 +1470,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,15 +1499,9 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>sälg</t>
@@ -1556,14 +1512,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1581,19 +1532,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118910566</v>
+        <v>118910547</v>
       </c>
       <c r="B9" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1621,10 +1567,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551758</v>
+        <v>551770</v>
       </c>
       <c r="R9" t="n">
-        <v>7144433</v>
+        <v>7144425</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1656,7 +1602,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1666,12 +1612,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>levande gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1698,53 +1644,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118910558</v>
+        <v>118910549</v>
       </c>
       <c r="B10" t="n">
-        <v>79628</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551738</v>
+        <v>551785</v>
       </c>
       <c r="R10" t="n">
-        <v>7144298</v>
+        <v>7144411</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1776,7 +1714,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1786,12 +1724,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,34 +1733,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1844,56 +1751,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118989617</v>
+        <v>118910566</v>
       </c>
       <c r="B11" t="n">
-        <v>74623</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551770</v>
+        <v>551758</v>
       </c>
       <c r="R11" t="n">
-        <v>7144431</v>
+        <v>7144433</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1917,12 +1816,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>levande gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1931,62 +1845,53 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118989667</v>
+        <v>118910567</v>
       </c>
       <c r="B12" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
@@ -1996,10 +1901,10 @@
         <v>551747</v>
       </c>
       <c r="R12" t="n">
-        <v>7144434</v>
+        <v>7144337</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2023,12 +1928,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2037,72 +1952,63 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118989629</v>
+        <v>133851066</v>
       </c>
       <c r="B13" t="n">
-        <v>77448</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Månsberget, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551770</v>
+        <v>551761</v>
       </c>
       <c r="R13" t="n">
-        <v>7144431</v>
+        <v>7144440</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2129,12 +2035,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-78</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2143,7 +2054,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2162,45 +2072,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126810186</v>
+        <v>118989617</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219880</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551691</v>
+        <v>551770</v>
       </c>
       <c r="R14" t="n">
-        <v>7144257</v>
+        <v>7144431</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2227,27 +2140,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>04:59</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>04:59</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Stort område med mycket plantor</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2256,50 +2154,51 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126810195</v>
+        <v>126810183</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2309,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551736</v>
+        <v>551799</v>
       </c>
       <c r="R15" t="n">
-        <v>7144262</v>
+        <v>7144430</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2344,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>04:48</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2354,12 +2253,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>04:48</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Stort område med många plantor utspridda</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2370,6 +2269,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2386,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126810193</v>
+        <v>118910556</v>
       </c>
       <c r="B16" t="n">
-        <v>98353</v>
+        <v>80468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,41 +2311,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>504</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551735</v>
+        <v>551770</v>
       </c>
       <c r="R16" t="n">
-        <v>7144261</v>
+        <v>7144425</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2455,27 +2368,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>04:49</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>04:49</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>12 överblommade plantor</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2484,8 +2397,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2502,10 +2441,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126810171</v>
+        <v>118910558</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>80468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,41 +2452,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551756</v>
+        <v>551738</v>
       </c>
       <c r="R17" t="n">
-        <v>7144388</v>
+        <v>7144298</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2571,27 +2509,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>9 överblommade plantor</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2600,8 +2538,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2618,45 +2582,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133851066</v>
+        <v>126810195</v>
       </c>
       <c r="B18" t="n">
-        <v>79366</v>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Månsberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551761</v>
+        <v>551736</v>
       </c>
       <c r="R18" t="n">
-        <v>7144440</v>
+        <v>7144262</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2683,17 +2647,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>04:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>04:48</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-78</t>
+          <t>Stort område med många plantor utspridda</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2708,15 +2682,1483 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126810186</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>551691</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7144257</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>04:59</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>04:59</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Stort område med mycket plantor</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126810187</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>551774</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7144273</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118910560</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>551764</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7144307</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>21 blomstänglar</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118910561</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>551765</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7144391</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>7 blommande ex</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118910562</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>551767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7144393</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>20 blommande ex lika många utan blomstängel</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118910563</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>551785</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7144411</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>27 blommande ex här, 3 andra lokaler på platsen dom var mindre</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118910564</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>551791</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7144425</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>11 blommande ex</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118910565</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>551773</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7144305</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>7 blomstänglar</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126810189</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>551785</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7144429</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>06:08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>06:08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 blomstängel många bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126810190</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>551766</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7144304</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>12 blomställningar från i fjol</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126810171</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>551756</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7144388</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>05:22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>05:22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>9 överblommade plantor</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>118989629</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Månsberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>551770</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7144431</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
           <t>Lukas Holmström</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>Lukas Holmström</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126810193</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126810194</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982914</t>
         </is>
       </c>
     </row>
@@ -1170,6 +1190,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118910550</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1271,6 +1296,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118989667</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1402,6 +1432,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126810169</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1529,6 +1564,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126810173</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1641,6 +1681,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118910547</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1748,6 +1793,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118910549</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1860,6 +1910,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118910566</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1967,6 +2022,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118910567</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2069,6 +2129,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851066</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2170,6 +2235,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118989617</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2297,6 +2367,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126810183</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2438,6 +2513,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118910556</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2579,6 +2659,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118910558</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2691,6 +2776,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126810195</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2803,6 +2893,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126810186</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2910,6 +3005,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126810187</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3044,6 +3144,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118910560</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3173,6 +3278,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118910561</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3307,6 +3417,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118910562</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3441,6 +3556,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118910563</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3575,6 +3695,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118910564</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3709,6 +3834,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118910565</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3821,6 +3951,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126810189</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3942,6 +4077,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126810190</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4058,6 +4198,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126810171</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4159,8 +4304,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118989629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>126810187</v>
       </c>
       <c r="B20" t="n">
-        <v>99456</v>
+        <v>99666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>126810187</v>
       </c>
       <c r="B20" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 17180-2024 artfynd.xlsx
+++ b/artfynd/A 17180-2024 artfynd.xlsx
@@ -2904,7 +2904,7 @@
         <v>126810187</v>
       </c>
       <c r="B20" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
